--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487901_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487901_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. ORLOV STURMAN MAURIN</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6201</v>
+        <v>3.5085</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4689</v>
+        <v>1.0918</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.8488</v>
+        <v>2.4167</v>
       </c>
       <c r="G2" t="n">
-        <v>2.409</v>
+        <v>2.828</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0826</v>
+        <v>2.4965</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6735</v>
+        <v>0.3315</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9853</v>
+        <v>2.7219</v>
       </c>
       <c r="K2" t="n">
-        <v>5.2015</v>
+        <v>2.6436</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.0784</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.5763</v>
+        <v>0.1061</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.119</v>
+        <v>-0.147</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.4573</v>
+        <v>0.2531</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0812</v>
+        <v>1.0406</v>
       </c>
       <c r="S2" t="n">
-        <v>0.974</v>
+        <v>0.4505</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3972</v>
+        <v>-0.1119</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5768</v>
+        <v>0.5624</v>
       </c>
       <c r="V2" t="n">
-        <v>0.237</v>
+        <v>0.23</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1675</v>
+        <v>-0.4776</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.9305</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>V. ORLOV STURMAN MAURIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3464</v>
+        <v>2.8075</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8123</v>
+        <v>4.8912</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5341</v>
+        <v>-2.0837</v>
       </c>
       <c r="G3" t="n">
-        <v>2.828</v>
+        <v>2.409</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4965</v>
+        <v>3.0826</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3315</v>
+        <v>-0.6735</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7219</v>
+        <v>5.9853</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6436</v>
+        <v>5.2015</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0784</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1061</v>
+        <v>-3.5763</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.147</v>
+        <v>-2.119</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2531</v>
+        <v>-1.4573</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0406</v>
+        <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2884</v>
+        <v>0.1615</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3915</v>
+        <v>-0.1804</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.3419</v>
       </c>
       <c r="V3" t="n">
-        <v>0.23</v>
+        <v>0.237</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.4776</v>
+        <v>1.1675</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7076</v>
+        <v>-0.9305</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MARIN ORTEGA</t>
+          <t>L. PAREJO CAMACHO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8509</v>
+        <v>1.4556</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8356</v>
+        <v>0.8884</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0153</v>
+        <v>0.5672</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3592</v>
+        <v>1.7157</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7395</v>
+        <v>0.0192</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6197</v>
+        <v>1.6965</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7147</v>
+        <v>1.8218</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1358</v>
+        <v>0.0192</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5788</v>
+        <v>1.8027</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3555</v>
+        <v>-0.1061</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3963</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0408</v>
+        <v>-0.1061</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2081</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0536</v>
+        <v>0.1561</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5153</v>
+        <v>0.1072</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5383</v>
+        <v>0.0489</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. PAREJO CAMACHO</t>
+          <t>Z. WILLIAMS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.319</v>
+        <v>1.1464</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7813</v>
+        <v>0.956</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.1903</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7157</v>
+        <v>0.3131</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0192</v>
+        <v>-0.5075</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6965</v>
+        <v>0.8205</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8218</v>
+        <v>1.5093</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0192</v>
+        <v>0.2642</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8027</v>
+        <v>1.245</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1061</v>
+        <v>-1.1962</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1061</v>
+        <v>-0.4245</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4162</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6244</v>
+        <v>1.4568</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0196</v>
+        <v>0.414</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0196</v>
+        <v>0.5135</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.0437</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.6275</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Z. WILLIAMS</t>
+          <t>A. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9484</v>
+        <v>0.8828</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6112</v>
+        <v>1.0436</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3371</v>
+        <v>-0.1609</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3131</v>
+        <v>1.3592</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5075</v>
+        <v>0.7395</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8205</v>
+        <v>0.6197</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5093</v>
+        <v>2.7147</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2642</v>
+        <v>2.1358</v>
       </c>
       <c r="L6" t="n">
-        <v>1.245</v>
+        <v>0.5788</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1962</v>
+        <v>-1.3555</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-1.3963</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4245</v>
+        <v>0.0408</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6244</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4568</v>
+        <v>0.8325</v>
       </c>
       <c r="S6" t="n">
-        <v>0.216</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4443</v>
+        <v>-0.2767</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6603</v>
+        <v>0.3621</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0437</v>
+        <v>-0.3538</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6275</v>
+        <v>-0.3538</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4873</v>
+        <v>0.8549</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6214</v>
+        <v>0.9009</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1341</v>
+        <v>-0.046</v>
       </c>
       <c r="G7" t="n">
         <v>1.2572</v>
@@ -1000,13 +1000,13 @@
         <v>1.2487</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5004</v>
+        <v>-0.1328</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5219</v>
+        <v>-0.2424</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0216</v>
+        <v>0.1096</v>
       </c>
       <c r="V7" t="n">
         <v>-0.4776</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1651</v>
+        <v>0.2818</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0664</v>
+        <v>2.1317</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2315</v>
+        <v>-1.8498</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9863</v>
@@ -1078,13 +1078,13 @@
         <v>2.0812</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7894</v>
+        <v>-0.3425</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.5129</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2113</v>
+        <v>0.1703</v>
       </c>
       <c r="V8" t="n">
         <v>-0.4706</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2311</v>
+        <v>-1.1658</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2631</v>
+        <v>-0.1979</v>
       </c>
       <c r="F9" t="n">
         <v>-0.968</v>
@@ -1156,10 +1156,10 @@
         <v>2.4974</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4815</v>
+        <v>0.5467</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.0033</v>
       </c>
       <c r="U9" t="n">
         <v>0.55</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6266</v>
+        <v>-3.986</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4712</v>
+        <v>-2.9773</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1554</v>
+        <v>-1.0086</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5549</v>
@@ -1234,13 +1234,13 @@
         <v>1.8731</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5793</v>
+        <v>0.0613</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.901</v>
+        <v>-0.4071</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3217</v>
+        <v>0.4685</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2843</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7241</v>
+        <v>-5.308</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5757</v>
+        <v>-1.189</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.1484</v>
+        <v>-4.119</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7822</v>
@@ -1312,13 +1312,13 @@
         <v>1.8731</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4495</v>
+        <v>-0.0334</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8358</v>
+        <v>-0.4491</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3863</v>
+        <v>0.4156</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2843</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1747999999999994</v>
+        <v>0.4777000000000005</v>
       </c>
       <c r="E12" t="n">
-        <v>6.887099999999999</v>
+        <v>7.539400000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.0619</v>
+        <v>-7.0618</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3668999999999998</v>
@@ -1390,13 +1390,13 @@
         <v>15.609</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7145000000000001</v>
+        <v>1.3669</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.8286</v>
+        <v>-2.1761</v>
       </c>
       <c r="U12" t="n">
-        <v>3.5432</v>
+        <v>3.5428</v>
       </c>
       <c r="V12" t="n">
         <v>-3.6442</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.8792</v>
+        <v>5.3142</v>
       </c>
       <c r="E13" t="n">
-        <v>5.4715</v>
+        <v>5.7929</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5923</v>
+        <v>-0.4787</v>
       </c>
       <c r="G13" t="n">
         <v>2.3313</v>
@@ -1468,13 +1468,13 @@
         <v>0.8325</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3053</v>
+        <v>0.1297</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7177</v>
+        <v>-0.3962</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4124</v>
+        <v>0.5259</v>
       </c>
       <c r="V13" t="n">
         <v>2.2289</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3737</v>
+        <v>4.9197</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9393</v>
+        <v>4.368</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4344</v>
+        <v>0.5518</v>
       </c>
       <c r="G14" t="n">
         <v>1.2885</v>
@@ -1546,13 +1546,13 @@
         <v>1.8731</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2851</v>
+        <v>0.261</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7705</v>
+        <v>-0.3419</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4854</v>
+        <v>0.6029</v>
       </c>
       <c r="V14" t="n">
         <v>1.7053</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>W. LEVEQUE</t>
+          <t>P. MENDES LIMA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.865</v>
+        <v>1.4273</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5185999999999999</v>
+        <v>2.5293</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3464</v>
+        <v>-1.102</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2992</v>
+        <v>3.0411</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7655</v>
+        <v>-0.036</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0646</v>
+        <v>3.0771</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3734</v>
+        <v>4.3109</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5986</v>
+        <v>1.8421</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7748</v>
+        <v>2.4689</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0742</v>
+        <v>-1.2699</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.364</v>
+        <v>-1.8781</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2898</v>
+        <v>0.6082</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.3299</v>
+        <v>-1.0406</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0812</v>
+        <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>1.693</v>
+        <v>-0.754</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2015</v>
+        <v>-0.741</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4915</v>
+        <v>-0.013</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1215</v>
+        <v>-0.8597</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2737</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1521</v>
+        <v>-0.8597</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. MENDES LIMA</t>
+          <t>W. LEVEQUE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3828</v>
+        <v>0.6706</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4222</v>
+        <v>-0.2315</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0394</v>
+        <v>0.9021</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0411</v>
+        <v>0.2992</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.036</v>
+        <v>-0.7655</v>
       </c>
       <c r="I16" t="n">
-        <v>3.0771</v>
+        <v>1.0646</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3109</v>
+        <v>2.3734</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8421</v>
+        <v>1.5986</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4689</v>
+        <v>0.7748</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2699</v>
+        <v>-2.0742</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8781</v>
+        <v>-2.364</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6082</v>
+        <v>0.2898</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0406</v>
+        <v>-3.3299</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0406</v>
+        <v>2.0812</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7985</v>
+        <v>0.4986</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8482</v>
+        <v>-0.5486</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0496</v>
+        <v>1.0472</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8597</v>
+        <v>1.1215</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2737</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8597</v>
+        <v>-0.1521</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5654</v>
+        <v>0.3907</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1012</v>
+        <v>0.7798</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5359</v>
+        <v>-0.3891</v>
       </c>
       <c r="G17" t="n">
         <v>1.483</v>
@@ -1780,13 +1780,13 @@
         <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0045</v>
+        <v>-0.1701</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0562</v>
+        <v>-0.3776</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0607</v>
+        <v>0.2075</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5059</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.342</v>
+        <v>-2.6047</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3399</v>
+        <v>-0.6614</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.002</v>
+        <v>-1.9433</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8222</v>
@@ -1936,13 +1936,13 @@
         <v>0.2081</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4802</v>
+        <v>0.2174</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5839</v>
+        <v>0.2624</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1037</v>
+        <v>-0.045</v>
       </c>
       <c r="V19" t="n">
         <v>-1.1675</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. CAMPENY LLOVERAS</t>
+          <t>A. LAFUENTE SISO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1792</v>
+        <v>-2.864</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8843</v>
+        <v>-1.1214</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2949</v>
+        <v>-1.7426</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.9102</v>
+        <v>-1.1288</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.034</v>
+        <v>0.4543</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.8763</v>
+        <v>-1.5831</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0078</v>
+        <v>1.5822</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9786</v>
+        <v>2.5284</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9864</v>
+        <v>-0.9463</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9025</v>
+        <v>-2.7109</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0126</v>
+        <v>-2.0741</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8899</v>
+        <v>-0.6368</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2081</v>
+        <v>-2.2893</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>-4.3705</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8325</v>
+        <v>2.0812</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6446</v>
+        <v>0.0163</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.6681</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0574</v>
+        <v>0.6844</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5838</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7513</v>
+        <v>2.3351</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1675</v>
+        <v>-1.7973</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. LAFUENTE SISO</t>
+          <t>P. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5236</v>
+        <v>-2.9252</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.55</v>
+        <v>-0.7771</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9736</v>
+        <v>-2.1481</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1288</v>
+        <v>-2.9102</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4543</v>
+        <v>-0.034</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5831</v>
+        <v>-2.8763</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5822</v>
+        <v>-1.0078</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5284</v>
+        <v>0.9786</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.9463</v>
+        <v>-1.9864</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7109</v>
+        <v>-1.9025</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0741</v>
+        <v>-1.0126</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6368</v>
+        <v>-0.8899</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.2893</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.3705</v>
+        <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0812</v>
+        <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6433</v>
+        <v>-0.3906</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0967</v>
+        <v>-0.48</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4535</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.5838</v>
       </c>
       <c r="W21" t="n">
-        <v>2.3351</v>
+        <v>1.7513</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7973</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9242</v>
+        <v>-3.5171</v>
       </c>
       <c r="E22" t="n">
         <v>-3.5515</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3727</v>
+        <v>0.0344</v>
       </c>
       <c r="G22" t="n">
         <v>-3.3579</v>
@@ -2170,13 +2170,13 @@
         <v>1.8731</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1501</v>
+        <v>0.2571</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1866</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0366</v>
+        <v>0.4437</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1746999999999996</v>
+        <v>0.8890999999999982</v>
       </c>
       <c r="E23" t="n">
-        <v>7.061900000000001</v>
+        <v>7.061900000000002</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.8871</v>
+        <v>-6.172600000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3669000000000002</v>
+        <v>0.3669000000000007</v>
       </c>
       <c r="H23" t="n">
         <v>-1.2253</v>
@@ -2227,7 +2227,7 @@
         <v>11.3301</v>
       </c>
       <c r="L23" t="n">
-        <v>6.0211</v>
+        <v>6.021100000000001</v>
       </c>
       <c r="M23" t="n">
         <v>-16.9843</v>
@@ -2248,13 +2248,13 @@
         <v>12.4872</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7143999999999999</v>
+        <v>0.0002000000000000335</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.5429</v>
+        <v>-3.5428</v>
       </c>
       <c r="U23" t="n">
-        <v>2.8286</v>
+        <v>3.543</v>
       </c>
       <c r="V23" t="n">
         <v>3.6442</v>
@@ -2263,7 +2263,7 @@
         <v>8.8627</v>
       </c>
       <c r="X23" t="n">
-        <v>-5.2184</v>
+        <v>-5.218400000000001</v>
       </c>
     </row>
   </sheetData>
